--- a/ECPRM1.xlsx
+++ b/ECPRM1.xlsx
@@ -61,7 +61,7 @@
     <t>10033572</t>
   </si>
   <si>
-    <t>PEDIASURE VAN KLG800</t>
+    <t>PDIASURE V KLG 800 G</t>
   </si>
   <si>
     <t>5</t>
